--- a/outputs/EVINV-POC-001/phase6/phase6-ppap-fai-readiness-index.xlsx
+++ b/outputs/EVINV-POC-001/phase6/phase6-ppap-fai-readiness-index.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Project: EVINV-POC-001 | Product: EV-INV-800 | Phase: 6 | Gate: 6 | Generated: 2026-08-18T21:33:34.786Z</v>
+        <v>Project: EVINV-POC-001 | Product: EV-INV-800 | Phase: 6 | Gate: 6 | Generated: 2026-08-19T02:42:14.046Z</v>
       </c>
     </row>
     <row r="4">
